--- a/vragen/puzzels_om_te_herbouwen.xlsx
+++ b/vragen/puzzels_om_te_herbouwen.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J465"/>
+  <dimension ref="A1:J472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17810,6 +17810,284 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>frontend_puzzles</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>library-031</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>135 × 1000000 = 135000000</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>456</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Hoeveel uur duurde het langste videogame-marathonrecord?</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>135</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0</v>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>frontend_puzzles</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>library-135</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>11 × 1000 = 11000</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>452</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Hoeveel marathons liep de persoon met het record voor de meeste marathons?</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>frontend_puzzles</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>library-212</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>1000 ÷ 100 = 10</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>1311</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Hoeveel jongleurs deden mee aan het grootste jongleerrecord?</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>breinkrakers</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>bk-154</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>8 × 135 − 900 = 180</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>456</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Hoeveel uur duurde het langste videogame-marathonrecord?</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>135</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>race_pool</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>pool-005</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>330 + 670 = 1000</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>452</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Hoeveel marathons liep de persoon met het record voor de meeste marathons?</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>race_pool</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>pool-049</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>99 + 36 = 135</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>456</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Hoeveel uur duurde het langste videogame-marathonrecord?</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>135</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>race_pool</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>pool-128</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>39000 ÷ 1000 = 39</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>1311</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Hoeveel jongleurs deden mee aan het grootste jongleerrecord?</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>recordantwoord gecorrigeerd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
